--- a/foody/test.xlsx
+++ b/foody/test.xlsx
@@ -8,24 +8,33 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin Data\PycharmProjects\pythonProject1\github\venv\foody\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B84B8AF-DDEF-464A-8C25-A9731D3BE1A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C16DEAF-E1A8-434D-B229-19A901853093}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="114">
   <si>
     <t>STT</t>
   </si>
@@ -331,6 +340,42 @@
   </si>
   <si>
     <t>220/17 hoang hoa tham, Phường Bình Lợi Trung, Thành phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>Location</t>
+  </si>
+  <si>
+    <t>10.8421216,106.672972</t>
+  </si>
+  <si>
+    <t>10.7519372,106.6656543</t>
+  </si>
+  <si>
+    <t>10.7519883,106.6656522</t>
+  </si>
+  <si>
+    <t>10.813533,106.66305</t>
+  </si>
+  <si>
+    <t>10.7616588,106.6679991</t>
+  </si>
+  <si>
+    <t>10.766824,106.692795</t>
+  </si>
+  <si>
+    <t>10.753464,106.684383</t>
+  </si>
+  <si>
+    <t>10.8358709,106.6288186</t>
+  </si>
+  <si>
+    <t>10.7651065,106.6628409</t>
+  </si>
+  <si>
+    <t>10.738154,106.717813</t>
+  </si>
+  <si>
+    <t>10.8094572,106.6858798</t>
   </si>
 </sst>
 </file>
@@ -648,10 +693,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q21"/>
+  <dimension ref="A1:R21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="6" max="6" width="22.140625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -668,43 +716,46 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
+        <v>102</v>
+      </c>
+      <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -720,44 +771,47 @@
       <c r="E2">
         <v>10</v>
       </c>
-      <c r="F2">
+      <c r="F2" t="s">
+        <v>103</v>
+      </c>
+      <c r="G2">
         <v>10.8421216</v>
       </c>
-      <c r="G2">
+      <c r="H2">
         <v>106.672972</v>
       </c>
-      <c r="H2">
+      <c r="I2">
         <v>1137.888323737415</v>
       </c>
-      <c r="I2" t="b">
-        <v>1</v>
-      </c>
       <c r="J2" t="b">
         <v>1</v>
       </c>
-      <c r="K2" t="s">
+      <c r="K2" t="b">
+        <v>1</v>
+      </c>
+      <c r="L2" t="s">
         <v>20</v>
       </c>
-      <c r="L2" t="s">
+      <c r="M2" t="s">
         <v>21</v>
       </c>
-      <c r="M2" t="s">
+      <c r="N2" t="s">
         <v>22</v>
       </c>
-      <c r="N2" t="s">
+      <c r="O2" t="s">
         <v>23</v>
       </c>
-      <c r="O2" t="s">
+      <c r="P2" t="s">
         <v>24</v>
       </c>
-      <c r="P2">
+      <c r="Q2">
         <v>10.8420465</v>
       </c>
-      <c r="Q2">
+      <c r="R2">
         <v>106.6729572</v>
       </c>
     </row>
-    <row r="3" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -773,44 +827,47 @@
       <c r="E3">
         <v>6.8639999999999999</v>
       </c>
-      <c r="F3">
-        <v>10.7519372</v>
+      <c r="F3" t="s">
+        <v>104</v>
       </c>
       <c r="G3">
-        <v>106.6656543</v>
+        <v>10.7519372</v>
       </c>
       <c r="H3">
+        <v>106.6656543</v>
+      </c>
+      <c r="I3">
         <v>1147.839528866908</v>
       </c>
-      <c r="I3" t="b">
-        <v>1</v>
-      </c>
       <c r="J3" t="b">
         <v>1</v>
       </c>
-      <c r="K3" t="s">
+      <c r="K3" t="b">
+        <v>1</v>
+      </c>
+      <c r="L3" t="s">
         <v>27</v>
       </c>
-      <c r="L3" t="s">
+      <c r="M3" t="s">
         <v>28</v>
       </c>
-      <c r="M3" t="s">
+      <c r="N3" t="s">
         <v>29</v>
       </c>
-      <c r="N3" t="s">
+      <c r="O3" t="s">
         <v>30</v>
       </c>
-      <c r="O3" t="s">
+      <c r="P3" t="s">
         <v>31</v>
       </c>
-      <c r="P3">
-        <v>10.7519372</v>
-      </c>
       <c r="Q3">
-        <v>106.6656543</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+        <v>10.7519372</v>
+      </c>
+      <c r="R3">
+        <v>106.6656543</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -826,44 +883,47 @@
       <c r="E4">
         <v>7.0780000000000003</v>
       </c>
-      <c r="F4">
-        <v>10.7519372</v>
+      <c r="F4" t="s">
+        <v>104</v>
       </c>
       <c r="G4">
-        <v>106.6656543</v>
+        <v>10.7519372</v>
       </c>
       <c r="H4">
+        <v>106.6656543</v>
+      </c>
+      <c r="I4">
         <v>1147.839528866908</v>
       </c>
-      <c r="I4" t="b">
-        <v>1</v>
-      </c>
       <c r="J4" t="b">
         <v>1</v>
       </c>
-      <c r="K4" t="s">
+      <c r="K4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L4" t="s">
         <v>27</v>
       </c>
-      <c r="L4" t="s">
+      <c r="M4" t="s">
         <v>28</v>
       </c>
-      <c r="M4" t="s">
+      <c r="N4" t="s">
         <v>29</v>
       </c>
-      <c r="N4" t="s">
+      <c r="O4" t="s">
         <v>30</v>
       </c>
-      <c r="O4" t="s">
+      <c r="P4" t="s">
         <v>31</v>
       </c>
-      <c r="P4">
-        <v>10.7519372</v>
-      </c>
       <c r="Q4">
-        <v>106.6656543</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+        <v>10.7519372</v>
+      </c>
+      <c r="R4">
+        <v>106.6656543</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -879,44 +939,47 @@
       <c r="E5">
         <v>6.532</v>
       </c>
-      <c r="F5">
-        <v>10.7519372</v>
+      <c r="F5" t="s">
+        <v>104</v>
       </c>
       <c r="G5">
-        <v>106.6656543</v>
+        <v>10.7519372</v>
       </c>
       <c r="H5">
+        <v>106.6656543</v>
+      </c>
+      <c r="I5">
         <v>1147.839528866908</v>
       </c>
-      <c r="I5" t="b">
-        <v>1</v>
-      </c>
       <c r="J5" t="b">
         <v>1</v>
       </c>
-      <c r="K5" t="s">
+      <c r="K5" t="b">
+        <v>1</v>
+      </c>
+      <c r="L5" t="s">
         <v>27</v>
       </c>
-      <c r="L5" t="s">
+      <c r="M5" t="s">
         <v>28</v>
       </c>
-      <c r="M5" t="s">
+      <c r="N5" t="s">
         <v>29</v>
       </c>
-      <c r="N5" t="s">
+      <c r="O5" t="s">
         <v>30</v>
       </c>
-      <c r="O5" t="s">
+      <c r="P5" t="s">
         <v>31</v>
       </c>
-      <c r="P5">
-        <v>10.7519372</v>
-      </c>
       <c r="Q5">
-        <v>106.6656543</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+        <v>10.7519372</v>
+      </c>
+      <c r="R5">
+        <v>106.6656543</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -932,44 +995,47 @@
       <c r="E6">
         <v>7.0419999999999998</v>
       </c>
-      <c r="F6">
-        <v>10.7519372</v>
+      <c r="F6" t="s">
+        <v>104</v>
       </c>
       <c r="G6">
-        <v>106.6656543</v>
+        <v>10.7519372</v>
       </c>
       <c r="H6">
+        <v>106.6656543</v>
+      </c>
+      <c r="I6">
         <v>1147.839528866908</v>
       </c>
-      <c r="I6" t="b">
-        <v>1</v>
-      </c>
       <c r="J6" t="b">
         <v>1</v>
       </c>
-      <c r="K6" t="s">
+      <c r="K6" t="b">
+        <v>1</v>
+      </c>
+      <c r="L6" t="s">
         <v>27</v>
       </c>
-      <c r="L6" t="s">
+      <c r="M6" t="s">
         <v>28</v>
       </c>
-      <c r="M6" t="s">
+      <c r="N6" t="s">
         <v>29</v>
       </c>
-      <c r="N6" t="s">
+      <c r="O6" t="s">
         <v>30</v>
       </c>
-      <c r="O6" t="s">
+      <c r="P6" t="s">
         <v>31</v>
       </c>
-      <c r="P6">
-        <v>10.7519372</v>
-      </c>
       <c r="Q6">
-        <v>106.6656543</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+        <v>10.7519372</v>
+      </c>
+      <c r="R6">
+        <v>106.6656543</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -985,44 +1051,47 @@
       <c r="E7">
         <v>6.484</v>
       </c>
-      <c r="F7">
-        <v>10.7519372</v>
+      <c r="F7" t="s">
+        <v>104</v>
       </c>
       <c r="G7">
-        <v>106.6656543</v>
+        <v>10.7519372</v>
       </c>
       <c r="H7">
+        <v>106.6656543</v>
+      </c>
+      <c r="I7">
         <v>1147.839528866908</v>
       </c>
-      <c r="I7" t="b">
-        <v>1</v>
-      </c>
       <c r="J7" t="b">
         <v>1</v>
       </c>
-      <c r="K7" t="s">
+      <c r="K7" t="b">
+        <v>1</v>
+      </c>
+      <c r="L7" t="s">
         <v>27</v>
       </c>
-      <c r="L7" t="s">
+      <c r="M7" t="s">
         <v>28</v>
       </c>
-      <c r="M7" t="s">
+      <c r="N7" t="s">
         <v>29</v>
       </c>
-      <c r="N7" t="s">
+      <c r="O7" t="s">
         <v>30</v>
       </c>
-      <c r="O7" t="s">
+      <c r="P7" t="s">
         <v>31</v>
       </c>
-      <c r="P7">
-        <v>10.7519372</v>
-      </c>
       <c r="Q7">
-        <v>106.6656543</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+        <v>10.7519372</v>
+      </c>
+      <c r="R7">
+        <v>106.6656543</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1038,44 +1107,47 @@
       <c r="E8">
         <v>7.1559999999999997</v>
       </c>
-      <c r="F8">
-        <v>10.7519372</v>
+      <c r="F8" t="s">
+        <v>104</v>
       </c>
       <c r="G8">
-        <v>106.6656543</v>
+        <v>10.7519372</v>
       </c>
       <c r="H8">
+        <v>106.6656543</v>
+      </c>
+      <c r="I8">
         <v>1147.839528866908</v>
       </c>
-      <c r="I8" t="b">
-        <v>1</v>
-      </c>
       <c r="J8" t="b">
         <v>1</v>
       </c>
-      <c r="K8" t="s">
+      <c r="K8" t="b">
+        <v>1</v>
+      </c>
+      <c r="L8" t="s">
         <v>27</v>
       </c>
-      <c r="L8" t="s">
+      <c r="M8" t="s">
         <v>28</v>
       </c>
-      <c r="M8" t="s">
+      <c r="N8" t="s">
         <v>29</v>
       </c>
-      <c r="N8" t="s">
+      <c r="O8" t="s">
         <v>30</v>
       </c>
-      <c r="O8" t="s">
+      <c r="P8" t="s">
         <v>31</v>
       </c>
-      <c r="P8">
-        <v>10.7519372</v>
-      </c>
       <c r="Q8">
-        <v>106.6656543</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+        <v>10.7519372</v>
+      </c>
+      <c r="R8">
+        <v>106.6656543</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1091,44 +1163,47 @@
       <c r="E9">
         <v>6.8360000000000003</v>
       </c>
-      <c r="F9">
-        <v>10.7519372</v>
+      <c r="F9" t="s">
+        <v>104</v>
       </c>
       <c r="G9">
-        <v>106.6656543</v>
+        <v>10.7519372</v>
       </c>
       <c r="H9">
+        <v>106.6656543</v>
+      </c>
+      <c r="I9">
         <v>1147.839528866908</v>
       </c>
-      <c r="I9" t="b">
-        <v>1</v>
-      </c>
       <c r="J9" t="b">
         <v>1</v>
       </c>
-      <c r="K9" t="s">
+      <c r="K9" t="b">
+        <v>1</v>
+      </c>
+      <c r="L9" t="s">
         <v>27</v>
       </c>
-      <c r="L9" t="s">
+      <c r="M9" t="s">
         <v>28</v>
       </c>
-      <c r="M9" t="s">
+      <c r="N9" t="s">
         <v>29</v>
       </c>
-      <c r="N9" t="s">
+      <c r="O9" t="s">
         <v>30</v>
       </c>
-      <c r="O9" t="s">
+      <c r="P9" t="s">
         <v>31</v>
       </c>
-      <c r="P9">
-        <v>10.7519372</v>
-      </c>
       <c r="Q9">
-        <v>106.6656543</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+        <v>10.7519372</v>
+      </c>
+      <c r="R9">
+        <v>106.6656543</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1144,44 +1219,47 @@
       <c r="E10">
         <v>6.89</v>
       </c>
-      <c r="F10">
-        <v>10.7519372</v>
+      <c r="F10" t="s">
+        <v>104</v>
       </c>
       <c r="G10">
-        <v>106.6656543</v>
+        <v>10.7519372</v>
       </c>
       <c r="H10">
+        <v>106.6656543</v>
+      </c>
+      <c r="I10">
         <v>1147.839528866908</v>
       </c>
-      <c r="I10" t="b">
-        <v>1</v>
-      </c>
       <c r="J10" t="b">
         <v>1</v>
       </c>
-      <c r="K10" t="s">
+      <c r="K10" t="b">
+        <v>1</v>
+      </c>
+      <c r="L10" t="s">
         <v>27</v>
       </c>
-      <c r="L10" t="s">
+      <c r="M10" t="s">
         <v>28</v>
       </c>
-      <c r="M10" t="s">
+      <c r="N10" t="s">
         <v>29</v>
       </c>
-      <c r="N10" t="s">
+      <c r="O10" t="s">
         <v>30</v>
       </c>
-      <c r="O10" t="s">
+      <c r="P10" t="s">
         <v>31</v>
       </c>
-      <c r="P10">
-        <v>10.7519372</v>
-      </c>
       <c r="Q10">
-        <v>106.6656543</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+        <v>10.7519372</v>
+      </c>
+      <c r="R10">
+        <v>106.6656543</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1197,44 +1275,47 @@
       <c r="E11">
         <v>7.0720000000000001</v>
       </c>
-      <c r="F11">
+      <c r="F11" t="s">
+        <v>105</v>
+      </c>
+      <c r="G11">
         <v>10.751988300000001</v>
       </c>
-      <c r="G11">
+      <c r="H11">
         <v>106.6656522</v>
       </c>
-      <c r="H11">
+      <c r="I11">
         <v>1147.833839065951</v>
       </c>
-      <c r="I11" t="b">
-        <v>1</v>
-      </c>
       <c r="J11" t="b">
         <v>1</v>
       </c>
-      <c r="K11" t="s">
+      <c r="K11" t="b">
+        <v>1</v>
+      </c>
+      <c r="L11" t="s">
         <v>42</v>
       </c>
-      <c r="L11" t="s">
+      <c r="M11" t="s">
         <v>43</v>
       </c>
-      <c r="M11" t="s">
+      <c r="N11" t="s">
         <v>41</v>
       </c>
-      <c r="N11" t="s">
+      <c r="O11" t="s">
         <v>44</v>
       </c>
-      <c r="O11" t="s">
+      <c r="P11" t="s">
         <v>45</v>
       </c>
-      <c r="P11">
+      <c r="Q11">
         <v>10.751988300000001</v>
       </c>
-      <c r="Q11">
+      <c r="R11">
         <v>106.6656522</v>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1250,44 +1331,47 @@
       <c r="E12">
         <v>6.6139999999999999</v>
       </c>
-      <c r="F12">
-        <v>10.7519372</v>
+      <c r="F12" t="s">
+        <v>104</v>
       </c>
       <c r="G12">
-        <v>106.6656543</v>
+        <v>10.7519372</v>
       </c>
       <c r="H12">
+        <v>106.6656543</v>
+      </c>
+      <c r="I12">
         <v>1147.839528866908</v>
       </c>
-      <c r="I12" t="b">
-        <v>1</v>
-      </c>
       <c r="J12" t="b">
         <v>1</v>
       </c>
-      <c r="K12" t="s">
+      <c r="K12" t="b">
+        <v>1</v>
+      </c>
+      <c r="L12" t="s">
         <v>27</v>
       </c>
-      <c r="L12" t="s">
+      <c r="M12" t="s">
         <v>28</v>
       </c>
-      <c r="M12" t="s">
+      <c r="N12" t="s">
         <v>29</v>
       </c>
-      <c r="N12" t="s">
+      <c r="O12" t="s">
         <v>30</v>
       </c>
-      <c r="O12" t="s">
+      <c r="P12" t="s">
         <v>31</v>
       </c>
-      <c r="P12">
-        <v>10.7519372</v>
-      </c>
       <c r="Q12">
-        <v>106.6656543</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+        <v>10.7519372</v>
+      </c>
+      <c r="R12">
+        <v>106.6656543</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1303,44 +1387,47 @@
       <c r="E13">
         <v>6.9580000000000002</v>
       </c>
-      <c r="F13">
-        <v>10.7519372</v>
+      <c r="F13" t="s">
+        <v>104</v>
       </c>
       <c r="G13">
-        <v>106.6656543</v>
+        <v>10.7519372</v>
       </c>
       <c r="H13">
+        <v>106.6656543</v>
+      </c>
+      <c r="I13">
         <v>1147.839528866908</v>
       </c>
-      <c r="I13" t="b">
-        <v>1</v>
-      </c>
       <c r="J13" t="b">
         <v>1</v>
       </c>
-      <c r="K13" t="s">
+      <c r="K13" t="b">
+        <v>1</v>
+      </c>
+      <c r="L13" t="s">
         <v>27</v>
       </c>
-      <c r="L13" t="s">
+      <c r="M13" t="s">
         <v>28</v>
       </c>
-      <c r="M13" t="s">
+      <c r="N13" t="s">
         <v>29</v>
       </c>
-      <c r="N13" t="s">
+      <c r="O13" t="s">
         <v>30</v>
       </c>
-      <c r="O13" t="s">
+      <c r="P13" t="s">
         <v>31</v>
       </c>
-      <c r="P13">
-        <v>10.7519372</v>
-      </c>
       <c r="Q13">
-        <v>106.6656543</v>
-      </c>
-    </row>
-    <row r="14" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+        <v>10.7519372</v>
+      </c>
+      <c r="R13">
+        <v>106.6656543</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1356,44 +1443,47 @@
       <c r="E14">
         <v>7.2220000000000004</v>
       </c>
-      <c r="F14">
+      <c r="F14" t="s">
+        <v>106</v>
+      </c>
+      <c r="G14">
         <v>10.813533</v>
       </c>
-      <c r="G14">
+      <c r="H14">
         <v>106.66305</v>
       </c>
-      <c r="H14">
+      <c r="I14">
         <v>1140.980491066575</v>
       </c>
-      <c r="I14" t="b">
-        <v>1</v>
-      </c>
       <c r="J14" t="b">
         <v>1</v>
       </c>
-      <c r="K14" t="s">
+      <c r="K14" t="b">
+        <v>1</v>
+      </c>
+      <c r="L14" t="s">
         <v>51</v>
       </c>
-      <c r="L14" t="s">
+      <c r="M14" t="s">
         <v>52</v>
       </c>
-      <c r="M14" t="s">
+      <c r="N14" t="s">
         <v>53</v>
       </c>
-      <c r="N14" t="s">
+      <c r="O14" t="s">
         <v>54</v>
       </c>
-      <c r="O14" t="s">
+      <c r="P14" t="s">
         <v>55</v>
       </c>
-      <c r="P14">
+      <c r="Q14">
         <v>10.813533</v>
       </c>
-      <c r="Q14">
+      <c r="R14">
         <v>106.66305</v>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1409,44 +1499,47 @@
       <c r="E15">
         <v>7.9980000000000002</v>
       </c>
-      <c r="F15">
+      <c r="F15" t="s">
+        <v>107</v>
+      </c>
+      <c r="G15">
         <v>10.761658799999999</v>
       </c>
-      <c r="G15">
+      <c r="H15">
         <v>106.6679991</v>
       </c>
-      <c r="H15">
+      <c r="I15">
         <v>1146.779390031709</v>
       </c>
-      <c r="I15" t="b">
-        <v>1</v>
-      </c>
       <c r="J15" t="b">
         <v>1</v>
       </c>
-      <c r="K15" t="s">
+      <c r="K15" t="b">
+        <v>1</v>
+      </c>
+      <c r="L15" t="s">
         <v>58</v>
       </c>
-      <c r="L15" t="s">
+      <c r="M15" t="s">
         <v>59</v>
       </c>
-      <c r="M15" t="s">
+      <c r="N15" t="s">
         <v>56</v>
       </c>
-      <c r="N15" t="s">
+      <c r="O15" t="s">
         <v>60</v>
       </c>
-      <c r="O15" t="s">
+      <c r="P15" t="s">
         <v>61</v>
       </c>
-      <c r="P15">
+      <c r="Q15">
         <v>10.761658799999999</v>
       </c>
-      <c r="Q15">
+      <c r="R15">
         <v>106.6679991</v>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
@@ -1462,44 +1555,47 @@
       <c r="E16">
         <v>7.2560000000000002</v>
       </c>
-      <c r="F16">
+      <c r="F16" t="s">
+        <v>108</v>
+      </c>
+      <c r="G16">
         <v>10.766824</v>
       </c>
-      <c r="G16">
+      <c r="H16">
         <v>106.692795</v>
       </c>
-      <c r="H16">
+      <c r="I16">
         <v>1146.411199124012</v>
       </c>
-      <c r="I16" t="b">
-        <v>1</v>
-      </c>
       <c r="J16" t="b">
         <v>1</v>
       </c>
-      <c r="K16" t="s">
+      <c r="K16" t="b">
+        <v>1</v>
+      </c>
+      <c r="L16" t="s">
         <v>65</v>
       </c>
-      <c r="L16" t="s">
+      <c r="M16" t="s">
         <v>66</v>
       </c>
-      <c r="M16" t="s">
+      <c r="N16" t="s">
         <v>67</v>
       </c>
-      <c r="N16" t="s">
+      <c r="O16" t="s">
         <v>68</v>
       </c>
-      <c r="O16" t="s">
+      <c r="P16" t="s">
         <v>69</v>
       </c>
-      <c r="P16">
+      <c r="Q16">
         <v>10.766826099999999</v>
       </c>
-      <c r="Q16">
+      <c r="R16">
         <v>106.6928104</v>
       </c>
     </row>
-    <row r="17" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
@@ -1515,44 +1611,47 @@
       <c r="E17">
         <v>10</v>
       </c>
-      <c r="F17">
+      <c r="F17" t="s">
+        <v>109</v>
+      </c>
+      <c r="G17">
         <v>10.753463999999999</v>
       </c>
-      <c r="G17">
+      <c r="H17">
         <v>106.684383</v>
       </c>
-      <c r="H17">
+      <c r="I17">
         <v>1147.8238368306061</v>
       </c>
-      <c r="I17" t="b">
-        <v>1</v>
-      </c>
       <c r="J17" t="b">
+        <v>1</v>
+      </c>
+      <c r="K17" t="b">
         <v>0</v>
       </c>
-      <c r="K17" t="s">
+      <c r="L17" t="s">
         <v>72</v>
       </c>
-      <c r="L17" t="s">
+      <c r="M17" t="s">
         <v>73</v>
       </c>
-      <c r="M17" t="s">
+      <c r="N17" t="s">
         <v>74</v>
       </c>
-      <c r="N17" t="s">
+      <c r="O17" t="s">
         <v>75</v>
       </c>
-      <c r="O17" t="s">
+      <c r="P17" t="s">
         <v>76</v>
       </c>
-      <c r="P17">
+      <c r="Q17">
         <v>10.7534574</v>
       </c>
-      <c r="Q17">
+      <c r="R17">
         <v>106.6844232</v>
       </c>
     </row>
-    <row r="18" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
@@ -1568,44 +1667,47 @@
       <c r="E18">
         <v>5.6920000000000002</v>
       </c>
-      <c r="F18">
+      <c r="F18" t="s">
+        <v>110</v>
+      </c>
+      <c r="G18">
         <v>10.8358709</v>
       </c>
-      <c r="G18">
+      <c r="H18">
         <v>106.6288186</v>
       </c>
-      <c r="H18">
+      <c r="I18">
         <v>1138.2274123922591</v>
       </c>
-      <c r="I18" t="b">
-        <v>1</v>
-      </c>
       <c r="J18" t="b">
         <v>1</v>
       </c>
-      <c r="K18" t="s">
+      <c r="K18" t="b">
+        <v>1</v>
+      </c>
+      <c r="L18" t="s">
         <v>80</v>
       </c>
-      <c r="L18" t="s">
+      <c r="M18" t="s">
         <v>81</v>
       </c>
-      <c r="M18" t="s">
+      <c r="N18" t="s">
         <v>82</v>
       </c>
-      <c r="N18" t="s">
+      <c r="O18" t="s">
         <v>83</v>
       </c>
-      <c r="O18" t="s">
+      <c r="P18" t="s">
         <v>84</v>
       </c>
-      <c r="P18">
+      <c r="Q18">
         <v>10.8358708896846</v>
       </c>
-      <c r="Q18">
+      <c r="R18">
         <v>106.6288186451286</v>
       </c>
     </row>
-    <row r="19" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
@@ -1621,44 +1723,47 @@
       <c r="E19">
         <v>10</v>
       </c>
-      <c r="F19">
+      <c r="F19" t="s">
+        <v>111</v>
+      </c>
+      <c r="G19">
         <v>10.7651065</v>
       </c>
-      <c r="G19">
+      <c r="H19">
         <v>106.66284090000001</v>
       </c>
-      <c r="H19">
+      <c r="I19">
         <v>1146.3547448746781</v>
       </c>
-      <c r="I19" t="b">
-        <v>1</v>
-      </c>
       <c r="J19" t="b">
         <v>1</v>
       </c>
-      <c r="K19" t="s">
+      <c r="K19" t="b">
+        <v>1</v>
+      </c>
+      <c r="L19" t="s">
         <v>87</v>
       </c>
-      <c r="L19" t="s">
+      <c r="M19" t="s">
         <v>88</v>
       </c>
-      <c r="M19" t="s">
+      <c r="N19" t="s">
         <v>85</v>
       </c>
-      <c r="N19" t="s">
+      <c r="O19" t="s">
         <v>60</v>
       </c>
-      <c r="O19" t="s">
+      <c r="P19" t="s">
         <v>89</v>
       </c>
-      <c r="P19">
+      <c r="Q19">
         <v>10.7651065</v>
       </c>
-      <c r="Q19">
+      <c r="R19">
         <v>106.66284090000001</v>
       </c>
     </row>
-    <row r="20" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
@@ -1674,44 +1779,47 @@
       <c r="E20">
         <v>7.16</v>
       </c>
-      <c r="F20">
+      <c r="F20" t="s">
+        <v>112</v>
+      </c>
+      <c r="G20">
         <v>10.738154</v>
       </c>
-      <c r="G20">
+      <c r="H20">
         <v>106.71781300000001</v>
       </c>
-      <c r="H20">
+      <c r="I20">
         <v>1149.8059861361751</v>
       </c>
-      <c r="I20" t="b">
-        <v>1</v>
-      </c>
       <c r="J20" t="b">
         <v>1</v>
       </c>
-      <c r="K20" t="s">
+      <c r="K20" t="b">
+        <v>1</v>
+      </c>
+      <c r="L20" t="s">
         <v>92</v>
       </c>
-      <c r="L20" t="s">
+      <c r="M20" t="s">
         <v>93</v>
       </c>
-      <c r="M20" t="s">
+      <c r="N20" t="s">
         <v>90</v>
       </c>
-      <c r="N20" t="s">
+      <c r="O20" t="s">
         <v>94</v>
       </c>
-      <c r="O20" t="s">
+      <c r="P20" t="s">
         <v>95</v>
       </c>
-      <c r="P20">
+      <c r="Q20">
         <v>10.738154</v>
       </c>
-      <c r="Q20">
+      <c r="R20">
         <v>106.71781300000001</v>
       </c>
     </row>
-    <row r="21" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
@@ -1727,40 +1835,43 @@
       <c r="E21">
         <v>10</v>
       </c>
-      <c r="F21">
+      <c r="F21" t="s">
+        <v>113</v>
+      </c>
+      <c r="G21">
         <v>10.809457200000001</v>
       </c>
-      <c r="G21">
+      <c r="H21">
         <v>106.6858798</v>
       </c>
-      <c r="H21">
+      <c r="I21">
         <v>1141.621280376608</v>
       </c>
-      <c r="I21" t="b">
-        <v>1</v>
-      </c>
       <c r="J21" t="b">
         <v>1</v>
       </c>
-      <c r="K21" t="s">
+      <c r="K21" t="b">
+        <v>1</v>
+      </c>
+      <c r="L21" t="s">
         <v>98</v>
       </c>
-      <c r="L21" t="s">
+      <c r="M21" t="s">
         <v>99</v>
       </c>
-      <c r="M21" t="s">
+      <c r="N21" t="s">
         <v>100</v>
       </c>
-      <c r="N21" t="s">
+      <c r="O21" t="s">
         <v>101</v>
       </c>
-      <c r="O21" t="s">
+      <c r="P21" t="s">
         <v>100</v>
       </c>
-      <c r="P21">
+      <c r="Q21">
         <v>10.8094626</v>
       </c>
-      <c r="Q21">
+      <c r="R21">
         <v>106.685897</v>
       </c>
     </row>
